--- a/PlanIT2026/developers/RH-F-04 Perfil y Descriptor de Puestos- IT-04A Programador Web Junior.xlsx
+++ b/PlanIT2026/developers/RH-F-04 Perfil y Descriptor de Puestos- IT-04A Programador Web Junior.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcela.Hernandez\rcj-it-manager\PlanIT2026\developers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8181E68-BEF3-493B-9A31-CF0034E18484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F733F4A-06E7-48AB-908B-D52408183AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IT-04A Programador Junior" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
   <si>
     <t>Fecha de creacion</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Conocimiento /Especialidades:</t>
   </si>
   <si>
-    <t>Conocimientos básicos en lenguajes de programación web (HTML, CSS, JavaScript, PHP o C#), manejo básico de bases de datos MySQL o MSSQL, fundamentos de control de versiones Git</t>
-  </si>
-  <si>
     <t>Rango de Edad: (Min - Max)</t>
   </si>
   <si>
@@ -416,6 +413,12 @@
   </si>
   <si>
     <t>Autorizado por:</t>
+  </si>
+  <si>
+    <t>Soporte tecnico a usuarios segun la necesidad de programas</t>
+  </si>
+  <si>
+    <t>Conocimientos básicos en lenguajes de programación web (HTML, CSS, JavaScript, Typescript, PHP o C#), manejo básico de bases de datos MySQL o MSSQL, fundamentos de control de versiones Git, SAP, PowerBI</t>
   </si>
 </sst>
 </file>
@@ -817,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1004,135 +1007,97 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1143,37 +1108,81 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1477,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
@@ -1512,383 +1521,383 @@
       <c r="A3" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="100"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="85"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="138" t="s">
+      <c r="C7" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="114" t="s">
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="95"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="109" t="s">
+      <c r="C8" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="120" t="s">
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="95"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="109" t="s">
+      <c r="C9" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="133" t="s">
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="134"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="134"/>
-      <c r="N9" s="135"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="120"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="121"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="120" t="s">
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="95"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="114" t="s">
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="95"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>6</v>
       </c>
-      <c r="C12" s="130" t="s">
+      <c r="C12" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="84"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="95"/>
     </row>
     <row r="13" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="112"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="84"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="95"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="99" t="s">
+      <c r="B14" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="100"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="85"/>
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="116" t="s">
+      <c r="B15" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="103"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="82"/>
     </row>
     <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="88"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="106"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="118"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="119"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="88"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="100"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="85"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="138" t="s">
+      <c r="C19" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="114" t="s">
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="95"/>
     </row>
     <row r="20" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>2</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="145" t="s">
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="146"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="146"/>
-      <c r="L20" s="146"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="147"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="110"/>
+    </row>
+    <row r="21" spans="2:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="148" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="146"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="146"/>
-      <c r="M21" s="146"/>
-      <c r="N21" s="147"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="109"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="110"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>4</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="120" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="95"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>5</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="107" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="9"/>
@@ -1897,42 +1906,42 @@
       <c r="B24" s="4">
         <v>6</v>
       </c>
-      <c r="C24" s="105" t="s">
+      <c r="C24" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>34</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>7</v>
       </c>
-      <c r="C25" s="105" t="s">
+      <c r="C25" s="107" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="15" t="s">
         <v>36</v>
-      </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="I25" s="16"/>
       <c r="J25" s="17"/>
@@ -1945,15 +1954,15 @@
       <c r="B26" s="4">
         <v>8</v>
       </c>
-      <c r="C26" s="105" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="106"/>
+      <c r="C26" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="93"/>
       <c r="H26" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I26" s="20"/>
       <c r="J26" s="21"/>
@@ -1963,189 +1972,189 @@
       <c r="N26" s="22"/>
     </row>
     <row r="27" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="112"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="95"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="99" t="s">
+      <c r="B28" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="85"/>
+    </row>
+    <row r="29" spans="2:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="100"/>
-    </row>
-    <row r="29" spans="2:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="86" t="s">
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="86" t="s">
+      <c r="G29" s="95"/>
+      <c r="H29" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="84"/>
-      <c r="H29" s="110" t="s">
+      <c r="I29" s="84"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="I29" s="83"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="113" t="s">
+      <c r="L29" s="84"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="L29" s="83"/>
-      <c r="M29" s="84"/>
-      <c r="N29" s="24" t="s">
+    </row>
+    <row r="30" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="114" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="129" t="s">
+      <c r="C30" s="81"/>
+      <c r="D30" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="90"/>
-      <c r="D30" s="25" t="s">
+      <c r="E30" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="F30" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="122" t="s">
+      <c r="G30" s="82"/>
+      <c r="H30" s="140" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="81"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="G30" s="103"/>
-      <c r="H30" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="I30" s="90"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="L30" s="28"/>
       <c r="M30" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="N30" s="96"/>
+    </row>
+    <row r="31" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="142" t="s">
         <v>50</v>
       </c>
-      <c r="N30" s="140"/>
-    </row>
-    <row r="31" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="97" t="s">
+      <c r="C31" s="90"/>
+      <c r="D31" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="88"/>
-      <c r="D31" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="32" t="s">
+      <c r="F31" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="G31" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="34" t="s">
+      <c r="H31" s="35" t="s">
         <v>54</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>55</v>
       </c>
       <c r="I31" s="36"/>
       <c r="J31" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L31" s="38"/>
       <c r="M31" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="N31" s="141"/>
+        <v>49</v>
+      </c>
+      <c r="N31" s="97"/>
     </row>
     <row r="32" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="142" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="90"/>
+      <c r="D32" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="88"/>
-      <c r="D32" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="33" t="s">
+      <c r="G32" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="39" t="s">
         <v>58</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="H32" s="39" t="s">
-        <v>59</v>
       </c>
       <c r="I32" s="40"/>
       <c r="J32" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L32" s="41"/>
       <c r="M32" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="N32" s="141"/>
+        <v>49</v>
+      </c>
+      <c r="N32" s="97"/>
     </row>
     <row r="33" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="42"/>
       <c r="D33" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="F33" s="33" t="s">
+      <c r="G33" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="39" t="s">
         <v>63</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>64</v>
       </c>
       <c r="I33" s="40"/>
       <c r="J33" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="147" t="s">
+        <v>64</v>
+      </c>
+      <c r="L33" s="90"/>
+      <c r="M33" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="L33" s="88"/>
-      <c r="M33" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="N33" s="141"/>
+      <c r="N33" s="97"/>
     </row>
     <row r="34" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="43"/>
@@ -2156,1044 +2165,1046 @@
         <v>14</v>
       </c>
       <c r="G34" s="46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H34" s="47" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="48"/>
       <c r="J34" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K34" s="49" t="s">
         <v>14</v>
       </c>
       <c r="L34" s="50"/>
       <c r="M34" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="142"/>
+        <v>53</v>
+      </c>
+      <c r="N34" s="98"/>
     </row>
     <row r="35" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="112"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="84"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="95"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="99" t="s">
+      <c r="B36" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="84"/>
+      <c r="N36" s="85"/>
+    </row>
+    <row r="37" spans="2:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="100"/>
-    </row>
-    <row r="37" spans="2:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="86" t="s">
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="110" t="s">
-        <v>69</v>
-      </c>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="95"/>
     </row>
     <row r="38" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="52"/>
-      <c r="C38" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="84"/>
+      <c r="C38" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="95"/>
       <c r="I38" s="51"/>
       <c r="J38" s="53"/>
-      <c r="K38" s="95" t="s">
+      <c r="K38" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="95"/>
     </row>
     <row r="39" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="53"/>
-      <c r="C39" s="102" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="103"/>
+      <c r="C39" s="132" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="82"/>
       <c r="I39" s="51"/>
       <c r="J39" s="53"/>
-      <c r="K39" s="95"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="84"/>
+      <c r="K39" s="116"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="95"/>
     </row>
     <row r="40" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="53"/>
-      <c r="C40" s="102" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="90"/>
-      <c r="E40" s="90"/>
-      <c r="F40" s="90"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="103"/>
+      <c r="C40" s="132" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="82"/>
       <c r="I40" s="51"/>
       <c r="J40" s="53"/>
-      <c r="K40" s="95"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="84"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="95"/>
     </row>
     <row r="41" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="53"/>
-      <c r="C41" s="102"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="103"/>
+      <c r="C41" s="132"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="82"/>
       <c r="I41" s="51"/>
       <c r="J41" s="53"/>
-      <c r="K41" s="95"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="84"/>
+      <c r="K41" s="116"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="95"/>
     </row>
     <row r="42" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="54"/>
-      <c r="C42" s="104"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="84"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="55"/>
       <c r="J42" s="54"/>
-      <c r="K42" s="128"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="84"/>
+      <c r="K42" s="130"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="95"/>
     </row>
     <row r="43" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="112"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="84"/>
+      <c r="B43" s="113"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="95"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="99" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="100"/>
+      <c r="B44" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="84"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="85"/>
     </row>
     <row r="45" spans="2:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="124" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="23" t="s">
+    </row>
+    <row r="46" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="100" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="98" t="s">
+      <c r="C46" s="84"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="84"/>
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="56" t="s">
+    </row>
+    <row r="47" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="100" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="98" t="s">
+      <c r="C47" s="84"/>
+      <c r="D47" s="84"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
+      <c r="M47" s="84"/>
+      <c r="N47" s="56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="83"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="98" t="s">
+      <c r="C48" s="84"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
+      <c r="M48" s="84"/>
+      <c r="N48" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="56" t="s">
+    </row>
+    <row r="49" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="100" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="49" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="98" t="s">
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="100" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="98" t="s">
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="J50" s="84"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="84"/>
+      <c r="M50" s="84"/>
+      <c r="N50" s="56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="98" t="s">
+      <c r="C51" s="84"/>
+      <c r="D51" s="84"/>
+      <c r="E51" s="84"/>
+      <c r="F51" s="84"/>
+      <c r="G51" s="84"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
+      <c r="M51" s="84"/>
+      <c r="N51" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="56" t="s">
+    </row>
+    <row r="52" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="100" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="52" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="98" t="s">
+      <c r="C52" s="84"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="84"/>
+      <c r="M52" s="84"/>
+      <c r="N52" s="56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="149"/>
+      <c r="D53" s="149"/>
+      <c r="E53" s="149"/>
+      <c r="F53" s="149"/>
+      <c r="G53" s="149"/>
+      <c r="H53" s="149"/>
+      <c r="I53" s="149"/>
+      <c r="J53" s="149"/>
+      <c r="K53" s="149"/>
+      <c r="L53" s="149"/>
+      <c r="M53" s="150"/>
+      <c r="N53" s="56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="98" t="s">
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="84"/>
+      <c r="I54" s="84"/>
+      <c r="J54" s="84"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="84"/>
+      <c r="M54" s="84"/>
+      <c r="N54" s="56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="141"/>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="84"/>
+      <c r="K55" s="84"/>
+      <c r="L55" s="84"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="57"/>
+    </row>
+    <row r="56" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="113"/>
+      <c r="C56" s="84"/>
+      <c r="D56" s="84"/>
+      <c r="E56" s="84"/>
+      <c r="F56" s="84"/>
+      <c r="G56" s="84"/>
+      <c r="H56" s="84"/>
+      <c r="I56" s="84"/>
+      <c r="J56" s="84"/>
+      <c r="K56" s="84"/>
+      <c r="L56" s="84"/>
+      <c r="M56" s="84"/>
+      <c r="N56" s="95"/>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B57" s="83"/>
+      <c r="C57" s="84"/>
+      <c r="D57" s="84"/>
+      <c r="E57" s="84"/>
+      <c r="F57" s="84"/>
+      <c r="G57" s="84"/>
+      <c r="H57" s="84"/>
+      <c r="I57" s="84"/>
+      <c r="J57" s="84"/>
+      <c r="K57" s="84"/>
+      <c r="L57" s="84"/>
+      <c r="M57" s="84"/>
+      <c r="N57" s="85"/>
+    </row>
+    <row r="58" spans="2:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="115"/>
+      <c r="C58" s="84"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="95"/>
+      <c r="F58" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="83"/>
-      <c r="N53" s="56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="111"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="83"/>
-      <c r="N54" s="57"/>
-    </row>
-    <row r="55" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="112"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="83"/>
-      <c r="N55" s="84"/>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B56" s="99"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="83"/>
-      <c r="N56" s="100"/>
-    </row>
-    <row r="57" spans="2:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="126"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="84"/>
-      <c r="F57" s="126" t="s">
+      <c r="G58" s="84"/>
+      <c r="H58" s="84"/>
+      <c r="I58" s="84"/>
+      <c r="J58" s="84"/>
+      <c r="K58" s="84"/>
+      <c r="L58" s="84"/>
+      <c r="M58" s="95"/>
+      <c r="N58" s="58"/>
+    </row>
+    <row r="59" spans="2:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="84"/>
-      <c r="N57" s="58"/>
-    </row>
-    <row r="58" spans="2:14" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="85" t="s">
+      <c r="C59" s="84"/>
+      <c r="D59" s="84"/>
+      <c r="E59" s="95"/>
+      <c r="F59" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="84"/>
-      <c r="F58" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="84"/>
-      <c r="N58" s="59">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="82" t="s">
-        <v>91</v>
-      </c>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="84"/>
+      <c r="G59" s="84"/>
+      <c r="H59" s="84"/>
+      <c r="I59" s="84"/>
+      <c r="J59" s="84"/>
+      <c r="K59" s="84"/>
+      <c r="L59" s="84"/>
+      <c r="M59" s="95"/>
       <c r="N59" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="2:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="85" t="s">
-        <v>92</v>
-      </c>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="G60" s="83"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="83"/>
-      <c r="J60" s="83"/>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="84"/>
+    <row r="60" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="84"/>
+      <c r="D60" s="84"/>
+      <c r="E60" s="95"/>
+      <c r="F60" s="112" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="84"/>
+      <c r="H60" s="84"/>
+      <c r="I60" s="84"/>
+      <c r="J60" s="84"/>
+      <c r="K60" s="84"/>
+      <c r="L60" s="84"/>
+      <c r="M60" s="95"/>
       <c r="N60" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="2:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="85" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" s="83"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="G61" s="83"/>
-      <c r="H61" s="83"/>
-      <c r="I61" s="83"/>
-      <c r="J61" s="83"/>
-      <c r="K61" s="83"/>
-      <c r="L61" s="83"/>
-      <c r="M61" s="84"/>
+    <row r="61" spans="2:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="84"/>
+      <c r="D61" s="84"/>
+      <c r="E61" s="95"/>
+      <c r="F61" s="112" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
+      <c r="I61" s="84"/>
+      <c r="J61" s="84"/>
+      <c r="K61" s="84"/>
+      <c r="L61" s="84"/>
+      <c r="M61" s="95"/>
       <c r="N61" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="2:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="84"/>
-      <c r="F62" s="82" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" s="83"/>
-      <c r="H62" s="83"/>
-      <c r="I62" s="83"/>
-      <c r="J62" s="83"/>
-      <c r="K62" s="83"/>
-      <c r="L62" s="83"/>
-      <c r="M62" s="84"/>
+    <row r="62" spans="2:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" s="84"/>
+      <c r="D62" s="84"/>
+      <c r="E62" s="95"/>
+      <c r="F62" s="112" t="s">
+        <v>94</v>
+      </c>
+      <c r="G62" s="84"/>
+      <c r="H62" s="84"/>
+      <c r="I62" s="84"/>
+      <c r="J62" s="84"/>
+      <c r="K62" s="84"/>
+      <c r="L62" s="84"/>
+      <c r="M62" s="95"/>
       <c r="N62" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="2:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="121" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" s="83"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="84"/>
-      <c r="F63" s="82" t="s">
-        <v>99</v>
-      </c>
-      <c r="G63" s="83"/>
-      <c r="H63" s="83"/>
-      <c r="I63" s="83"/>
-      <c r="J63" s="83"/>
-      <c r="K63" s="83"/>
-      <c r="L63" s="83"/>
-      <c r="M63" s="84"/>
+    <row r="63" spans="2:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="84"/>
+      <c r="D63" s="84"/>
+      <c r="E63" s="95"/>
+      <c r="F63" s="112" t="s">
+        <v>96</v>
+      </c>
+      <c r="G63" s="84"/>
+      <c r="H63" s="84"/>
+      <c r="I63" s="84"/>
+      <c r="J63" s="84"/>
+      <c r="K63" s="84"/>
+      <c r="L63" s="84"/>
+      <c r="M63" s="95"/>
       <c r="N63" s="59">
         <v>25</v>
       </c>
     </row>
     <row r="64" spans="2:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="85" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="83"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="84"/>
-      <c r="F64" s="82" t="s">
-        <v>101</v>
-      </c>
-      <c r="G64" s="83"/>
-      <c r="H64" s="83"/>
-      <c r="I64" s="83"/>
-      <c r="J64" s="83"/>
-      <c r="K64" s="83"/>
-      <c r="L64" s="83"/>
-      <c r="M64" s="84"/>
+      <c r="B64" s="134" t="s">
+        <v>97</v>
+      </c>
+      <c r="C64" s="84"/>
+      <c r="D64" s="84"/>
+      <c r="E64" s="95"/>
+      <c r="F64" s="112" t="s">
+        <v>98</v>
+      </c>
+      <c r="G64" s="84"/>
+      <c r="H64" s="84"/>
+      <c r="I64" s="84"/>
+      <c r="J64" s="84"/>
+      <c r="K64" s="84"/>
+      <c r="L64" s="84"/>
+      <c r="M64" s="95"/>
       <c r="N64" s="59">
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="85"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="83"/>
-      <c r="H65" s="83"/>
-      <c r="I65" s="83"/>
-      <c r="J65" s="83"/>
-      <c r="K65" s="83"/>
-      <c r="L65" s="83"/>
-      <c r="M65" s="84"/>
-      <c r="N65" s="59"/>
-    </row>
-    <row r="66" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="85"/>
-      <c r="C66" s="83"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="84"/>
-      <c r="F66" s="143"/>
-      <c r="G66" s="83"/>
-      <c r="H66" s="83"/>
-      <c r="I66" s="83"/>
-      <c r="J66" s="83"/>
-      <c r="K66" s="83"/>
-      <c r="L66" s="83"/>
-      <c r="M66" s="84"/>
+    <row r="65" spans="1:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="84"/>
+      <c r="D65" s="84"/>
+      <c r="E65" s="95"/>
+      <c r="F65" s="112" t="s">
+        <v>100</v>
+      </c>
+      <c r="G65" s="84"/>
+      <c r="H65" s="84"/>
+      <c r="I65" s="84"/>
+      <c r="J65" s="84"/>
+      <c r="K65" s="84"/>
+      <c r="L65" s="84"/>
+      <c r="M65" s="95"/>
+      <c r="N65" s="59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="94"/>
+      <c r="C66" s="84"/>
+      <c r="D66" s="84"/>
+      <c r="E66" s="95"/>
+      <c r="F66" s="112"/>
+      <c r="G66" s="84"/>
+      <c r="H66" s="84"/>
+      <c r="I66" s="84"/>
+      <c r="J66" s="84"/>
+      <c r="K66" s="84"/>
+      <c r="L66" s="84"/>
+      <c r="M66" s="95"/>
       <c r="N66" s="59"/>
     </row>
-    <row r="67" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="60"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="90"/>
-      <c r="E67" s="90"/>
-      <c r="F67" s="90"/>
-      <c r="G67" s="90"/>
-      <c r="H67" s="90"/>
-      <c r="I67" s="90"/>
-      <c r="J67" s="90"/>
-      <c r="K67" s="90"/>
-      <c r="L67" s="90"/>
-      <c r="M67" s="90"/>
-      <c r="N67" s="91"/>
-      <c r="O67" s="60"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="94"/>
+      <c r="C67" s="84"/>
+      <c r="D67" s="84"/>
+      <c r="E67" s="95"/>
+      <c r="F67" s="101"/>
+      <c r="G67" s="84"/>
+      <c r="H67" s="84"/>
+      <c r="I67" s="84"/>
+      <c r="J67" s="84"/>
+      <c r="K67" s="84"/>
+      <c r="L67" s="84"/>
+      <c r="M67" s="95"/>
+      <c r="N67" s="59"/>
+    </row>
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="60"/>
-      <c r="B68" s="101"/>
-      <c r="C68" s="83"/>
-      <c r="D68" s="83"/>
-      <c r="E68" s="83"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="131" t="s">
+      <c r="B68" s="127"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="81"/>
+      <c r="L68" s="81"/>
+      <c r="M68" s="81"/>
+      <c r="N68" s="128"/>
+      <c r="O68" s="60"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="60"/>
+      <c r="B69" s="126"/>
+      <c r="C69" s="84"/>
+      <c r="D69" s="84"/>
+      <c r="E69" s="84"/>
+      <c r="F69" s="95"/>
+      <c r="G69" s="118" t="s">
+        <v>101</v>
+      </c>
+      <c r="H69" s="84"/>
+      <c r="I69" s="84"/>
+      <c r="J69" s="84"/>
+      <c r="K69" s="84"/>
+      <c r="L69" s="84"/>
+      <c r="M69" s="95"/>
+      <c r="N69" s="61"/>
+      <c r="O69" s="60"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B70" s="33"/>
+      <c r="C70" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="H68" s="83"/>
-      <c r="I68" s="83"/>
-      <c r="J68" s="83"/>
-      <c r="K68" s="83"/>
-      <c r="L68" s="83"/>
-      <c r="M68" s="84"/>
-      <c r="N68" s="61"/>
-      <c r="O68" s="60"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B69" s="33"/>
-      <c r="C69" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="63"/>
-      <c r="H69" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="I69" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="J69" s="40"/>
-      <c r="K69" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="L69" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="M69" s="34"/>
-      <c r="N69" s="137"/>
-    </row>
-    <row r="70" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="33"/>
-      <c r="C70" s="62" t="s">
-        <v>108</v>
       </c>
       <c r="D70" s="62"/>
       <c r="E70" s="62"/>
       <c r="F70" s="63"/>
       <c r="H70" s="42" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J70" s="40"/>
       <c r="K70" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="L70" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="L70" s="42" t="s">
+      <c r="M70" s="34"/>
+      <c r="N70" s="136"/>
+    </row>
+    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="33"/>
+      <c r="C71" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="M70" s="34"/>
-      <c r="N70" s="93"/>
-    </row>
-    <row r="71" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="64"/>
-      <c r="C71" s="62"/>
       <c r="D71" s="62"/>
       <c r="E71" s="62"/>
       <c r="F71" s="63"/>
-      <c r="G71" s="65"/>
-      <c r="H71" s="66" t="s">
+      <c r="H71" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="I71" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="J71" s="40"/>
+      <c r="K71" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="L71" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="M71" s="34"/>
+      <c r="N71" s="137"/>
+    </row>
+    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="64"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="62"/>
+      <c r="E72" s="62"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="65"/>
+      <c r="H72" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="I72" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" s="48"/>
+      <c r="K72" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="L72" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="M72" s="46"/>
+      <c r="N72" s="138"/>
+    </row>
+    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="69"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="69"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="50"/>
+      <c r="M73" s="69"/>
+      <c r="N73" s="71"/>
+    </row>
+    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="104"/>
+      <c r="C74" s="87"/>
+      <c r="D74" s="87"/>
+      <c r="E74" s="87"/>
+      <c r="F74" s="87"/>
+      <c r="G74" s="87"/>
+      <c r="H74" s="87"/>
+      <c r="I74" s="87"/>
+      <c r="J74" s="87"/>
+      <c r="K74" s="87"/>
+      <c r="L74" s="87"/>
+      <c r="M74" s="87"/>
+      <c r="N74" s="88"/>
+    </row>
+    <row r="75" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I71" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="J71" s="48"/>
-      <c r="K71" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="L71" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="M71" s="46"/>
-      <c r="N71" s="94"/>
-    </row>
-    <row r="72" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="43"/>
-      <c r="C72" s="44"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="50"/>
-      <c r="M72" s="69"/>
-      <c r="N72" s="71"/>
-    </row>
-    <row r="73" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="144"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="81"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="81"/>
-      <c r="J73" s="81"/>
-      <c r="K73" s="81"/>
-      <c r="L73" s="81"/>
-      <c r="M73" s="81"/>
-      <c r="N73" s="119"/>
-    </row>
-    <row r="74" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="89" t="s">
+      <c r="C75" s="81"/>
+      <c r="D75" s="81"/>
+      <c r="E75" s="81"/>
+      <c r="F75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="81"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="81"/>
+      <c r="L75" s="81"/>
+      <c r="M75" s="81"/>
+      <c r="N75" s="128"/>
+    </row>
+    <row r="76" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="90"/>
-      <c r="D74" s="90"/>
-      <c r="E74" s="90"/>
-      <c r="F74" s="90"/>
-      <c r="G74" s="90"/>
-      <c r="H74" s="90"/>
-      <c r="I74" s="90"/>
-      <c r="J74" s="90"/>
-      <c r="K74" s="90"/>
-      <c r="L74" s="90"/>
-      <c r="M74" s="90"/>
-      <c r="N74" s="91"/>
-    </row>
-    <row r="75" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="101" t="s">
+      <c r="C76" s="84"/>
+      <c r="D76" s="84"/>
+      <c r="E76" s="84"/>
+      <c r="F76" s="95"/>
+      <c r="G76" s="126" t="s">
+        <v>101</v>
+      </c>
+      <c r="H76" s="84"/>
+      <c r="I76" s="84"/>
+      <c r="J76" s="84"/>
+      <c r="K76" s="84"/>
+      <c r="L76" s="84"/>
+      <c r="M76" s="95"/>
+      <c r="N76" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="84"/>
-      <c r="G75" s="101" t="s">
-        <v>102</v>
-      </c>
-      <c r="H75" s="83"/>
-      <c r="I75" s="83"/>
-      <c r="J75" s="83"/>
-      <c r="K75" s="83"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="84"/>
-      <c r="N75" s="61" t="s">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B77" s="33"/>
+      <c r="C77" s="106"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="84"/>
+      <c r="F77" s="84"/>
+      <c r="G77" s="135" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="81"/>
+      <c r="I77" s="73" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B76" s="33"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="125" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="90"/>
-      <c r="I76" s="73" t="s">
+      <c r="J77" s="74"/>
+      <c r="K77" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="J76" s="74"/>
-      <c r="K76" s="73" t="s">
+      <c r="L77" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="L76" s="73" t="s">
+      <c r="M77" s="29"/>
+      <c r="N77" s="148"/>
+    </row>
+    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="33"/>
+      <c r="C78" s="106" t="s">
         <v>116</v>
       </c>
-      <c r="M76" s="29"/>
-      <c r="N76" s="92"/>
-    </row>
-    <row r="77" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="33"/>
-      <c r="C77" s="96" t="s">
+      <c r="D78" s="84"/>
+      <c r="E78" s="84"/>
+      <c r="F78" s="84"/>
+      <c r="G78" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="D77" s="83"/>
-      <c r="E77" s="83"/>
-      <c r="F77" s="83"/>
-      <c r="G77" s="115" t="s">
-        <v>118</v>
-      </c>
-      <c r="H77" s="88"/>
-      <c r="I77" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="J77" s="40"/>
-      <c r="K77" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="L77" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="M77" s="34"/>
-      <c r="N77" s="93"/>
-    </row>
-    <row r="78" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="30"/>
-      <c r="C78" s="72" t="s">
-        <v>119</v>
-      </c>
-      <c r="D78" s="72"/>
-      <c r="E78" s="72"/>
-      <c r="F78" s="72"/>
-      <c r="G78" s="115" t="s">
-        <v>118</v>
-      </c>
-      <c r="H78" s="88"/>
+      <c r="H78" s="90"/>
       <c r="I78" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J78" s="40"/>
       <c r="K78" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L78" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M78" s="34"/>
-      <c r="N78" s="93"/>
+      <c r="N78" s="137"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="30"/>
       <c r="C79" s="72" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D79" s="72"/>
       <c r="E79" s="72"/>
       <c r="F79" s="72"/>
-      <c r="G79" s="115" t="s">
-        <v>118</v>
-      </c>
-      <c r="H79" s="88"/>
+      <c r="G79" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="H79" s="90"/>
       <c r="I79" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J79" s="40"/>
       <c r="K79" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L79" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M79" s="34"/>
-      <c r="N79" s="93"/>
+      <c r="N79" s="137"/>
     </row>
     <row r="80" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="30"/>
       <c r="C80" s="72" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D80" s="72"/>
       <c r="E80" s="72"/>
       <c r="F80" s="72"/>
-      <c r="G80" s="115" t="s">
-        <v>118</v>
-      </c>
-      <c r="H80" s="88"/>
+      <c r="G80" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="H80" s="90"/>
       <c r="I80" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J80" s="40"/>
       <c r="K80" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L80" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M80" s="34"/>
-      <c r="N80" s="93"/>
+      <c r="N80" s="137"/>
     </row>
     <row r="81" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="30"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
-      <c r="F81" s="83"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="81"/>
-      <c r="I81" s="67"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="67"/>
-      <c r="L81" s="67"/>
-      <c r="M81" s="46"/>
-      <c r="N81" s="94"/>
+      <c r="C81" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" s="90"/>
+      <c r="I81" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="J81" s="40"/>
+      <c r="K81" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="M81" s="34"/>
+      <c r="N81" s="137"/>
     </row>
     <row r="82" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="43"/>
-      <c r="C82" s="44"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="69"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="69"/>
-      <c r="K82" s="70"/>
-      <c r="L82" s="50"/>
-      <c r="M82" s="69"/>
-      <c r="N82" s="71"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="106"/>
+      <c r="D82" s="84"/>
+      <c r="E82" s="84"/>
+      <c r="F82" s="84"/>
+      <c r="G82" s="146"/>
+      <c r="H82" s="87"/>
+      <c r="I82" s="67"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="67"/>
+      <c r="L82" s="67"/>
+      <c r="M82" s="46"/>
+      <c r="N82" s="138"/>
     </row>
     <row r="83" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="136" t="s">
+      <c r="B83" s="43"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="69"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="50"/>
+      <c r="M83" s="69"/>
+      <c r="N83" s="71"/>
+    </row>
+    <row r="84" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="122" t="s">
+        <v>121</v>
+      </c>
+      <c r="C84" s="84"/>
+      <c r="D84" s="84"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="84"/>
+      <c r="H84" s="84"/>
+      <c r="I84" s="84"/>
+      <c r="J84" s="84"/>
+      <c r="K84" s="84"/>
+      <c r="L84" s="84"/>
+      <c r="M84" s="84"/>
+      <c r="N84" s="85"/>
+    </row>
+    <row r="85" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="83"/>
-      <c r="F83" s="83"/>
-      <c r="G83" s="83"/>
-      <c r="H83" s="83"/>
-      <c r="I83" s="83"/>
-      <c r="J83" s="83"/>
-      <c r="K83" s="83"/>
-      <c r="L83" s="83"/>
-      <c r="M83" s="83"/>
-      <c r="N83" s="100"/>
-    </row>
-    <row r="84" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="139" t="s">
-        <v>123</v>
-      </c>
-      <c r="C84" s="88"/>
-      <c r="D84" s="88"/>
-      <c r="E84" s="88"/>
-      <c r="F84" s="88"/>
-      <c r="G84" s="88"/>
-      <c r="H84" s="88"/>
-      <c r="I84" s="88"/>
-      <c r="J84" s="88"/>
-      <c r="K84" s="88"/>
-      <c r="L84" s="88"/>
-      <c r="M84" s="88"/>
-      <c r="N84" s="88"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B85" s="88"/>
-      <c r="C85" s="88"/>
-      <c r="D85" s="88"/>
-      <c r="E85" s="88"/>
-      <c r="F85" s="88"/>
-      <c r="G85" s="88"/>
-      <c r="H85" s="88"/>
-      <c r="I85" s="88"/>
-      <c r="J85" s="88"/>
-      <c r="K85" s="88"/>
-      <c r="L85" s="88"/>
-      <c r="M85" s="88"/>
-      <c r="N85" s="88"/>
+      <c r="C85" s="90"/>
+      <c r="D85" s="90"/>
+      <c r="E85" s="90"/>
+      <c r="F85" s="90"/>
+      <c r="G85" s="90"/>
+      <c r="H85" s="90"/>
+      <c r="I85" s="90"/>
+      <c r="J85" s="90"/>
+      <c r="K85" s="90"/>
+      <c r="L85" s="90"/>
+      <c r="M85" s="90"/>
+      <c r="N85" s="90"/>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B86" s="88"/>
-      <c r="C86" s="88"/>
-      <c r="D86" s="88"/>
-      <c r="E86" s="88"/>
-      <c r="F86" s="88"/>
-      <c r="G86" s="88"/>
-      <c r="H86" s="88"/>
-      <c r="I86" s="88"/>
-      <c r="J86" s="88"/>
-      <c r="K86" s="88"/>
-      <c r="L86" s="88"/>
-      <c r="M86" s="88"/>
-      <c r="N86" s="88"/>
+      <c r="B86" s="90"/>
+      <c r="C86" s="90"/>
+      <c r="D86" s="90"/>
+      <c r="E86" s="90"/>
+      <c r="F86" s="90"/>
+      <c r="G86" s="90"/>
+      <c r="H86" s="90"/>
+      <c r="I86" s="90"/>
+      <c r="J86" s="90"/>
+      <c r="K86" s="90"/>
+      <c r="L86" s="90"/>
+      <c r="M86" s="90"/>
+      <c r="N86" s="90"/>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B87" s="75"/>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="75"/>
-      <c r="F87" s="75"/>
-      <c r="G87" s="75"/>
-      <c r="H87" s="75"/>
-      <c r="I87" s="75"/>
-      <c r="J87" s="75"/>
-      <c r="K87" s="75"/>
-      <c r="L87" s="75"/>
-      <c r="M87" s="75"/>
-      <c r="N87" s="75"/>
-    </row>
-    <row r="88" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="90"/>
+      <c r="C87" s="90"/>
+      <c r="D87" s="90"/>
+      <c r="E87" s="90"/>
+      <c r="F87" s="90"/>
+      <c r="G87" s="90"/>
+      <c r="H87" s="90"/>
+      <c r="I87" s="90"/>
+      <c r="J87" s="90"/>
+      <c r="K87" s="90"/>
+      <c r="L87" s="90"/>
+      <c r="M87" s="90"/>
+      <c r="N87" s="90"/>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B88" s="75"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
-      <c r="F88" s="76"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
       <c r="G88" s="75"/>
       <c r="H88" s="75"/>
       <c r="I88" s="75"/>
       <c r="J88" s="75"/>
-      <c r="K88" s="76"/>
-      <c r="L88" s="76"/>
-      <c r="M88" s="76"/>
+      <c r="K88" s="75"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="75"/>
       <c r="N88" s="75"/>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="75"/>
-      <c r="C89" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="D89" s="75"/>
-      <c r="E89" s="75"/>
-      <c r="F89" s="75"/>
+      <c r="C89" s="76"/>
+      <c r="D89" s="76"/>
+      <c r="E89" s="76"/>
+      <c r="F89" s="76"/>
       <c r="G89" s="75"/>
       <c r="H89" s="75"/>
       <c r="I89" s="75"/>
       <c r="J89" s="75"/>
-      <c r="K89" s="75" t="s">
-        <v>125</v>
-      </c>
-      <c r="L89" s="75"/>
-      <c r="M89" s="75"/>
+      <c r="K89" s="76"/>
+      <c r="L89" s="76"/>
+      <c r="M89" s="76"/>
       <c r="N89" s="75"/>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B90" s="75"/>
-      <c r="C90" s="75"/>
+      <c r="C90" s="75" t="s">
+        <v>123</v>
+      </c>
       <c r="D90" s="75"/>
       <c r="E90" s="75"/>
       <c r="F90" s="75"/>
@@ -3201,7 +3212,9 @@
       <c r="H90" s="75"/>
       <c r="I90" s="75"/>
       <c r="J90" s="75"/>
-      <c r="K90" s="75"/>
+      <c r="K90" s="75" t="s">
+        <v>124</v>
+      </c>
       <c r="L90" s="75"/>
       <c r="M90" s="75"/>
       <c r="N90" s="75"/>
@@ -3251,7 +3264,7 @@
       <c r="M93" s="75"/>
       <c r="N93" s="75"/>
     </row>
-    <row r="94" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B94" s="75"/>
       <c r="C94" s="75"/>
       <c r="D94" s="75"/>
@@ -3266,7 +3279,7 @@
       <c r="M94" s="75"/>
       <c r="N94" s="75"/>
     </row>
-    <row r="95" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="75"/>
       <c r="C95" s="75"/>
       <c r="D95" s="75"/>
@@ -3296,7 +3309,7 @@
       <c r="M96" s="75"/>
       <c r="N96" s="75"/>
     </row>
-    <row r="97" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="75"/>
       <c r="C97" s="75"/>
       <c r="D97" s="75"/>
@@ -3311,7 +3324,7 @@
       <c r="M97" s="75"/>
       <c r="N97" s="75"/>
     </row>
-    <row r="98" spans="1:15" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="75"/>
       <c r="C98" s="75"/>
       <c r="D98" s="75"/>
@@ -3326,102 +3339,100 @@
       <c r="M98" s="75"/>
       <c r="N98" s="75"/>
     </row>
-    <row r="99" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="77"/>
-      <c r="B99" s="127"/>
-      <c r="C99" s="90"/>
-      <c r="D99" s="90"/>
-      <c r="E99" s="90"/>
-      <c r="F99" s="103"/>
-      <c r="G99" s="127"/>
-      <c r="H99" s="90"/>
-      <c r="I99" s="90"/>
-      <c r="J99" s="90"/>
-      <c r="K99" s="103"/>
-      <c r="L99" s="127"/>
-      <c r="M99" s="90"/>
-      <c r="N99" s="103"/>
-      <c r="O99" s="78"/>
-    </row>
-    <row r="100" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="78"/>
-      <c r="B100" s="117"/>
-      <c r="C100" s="88"/>
-      <c r="D100" s="88"/>
-      <c r="E100" s="88"/>
-      <c r="F100" s="106"/>
-      <c r="G100" s="117"/>
-      <c r="H100" s="88"/>
-      <c r="I100" s="88"/>
-      <c r="J100" s="88"/>
-      <c r="K100" s="106"/>
-      <c r="L100" s="117"/>
-      <c r="M100" s="88"/>
-      <c r="N100" s="106"/>
+    <row r="99" spans="1:15" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="75"/>
+      <c r="I99" s="75"/>
+      <c r="J99" s="75"/>
+      <c r="K99" s="75"/>
+      <c r="L99" s="75"/>
+      <c r="M99" s="75"/>
+      <c r="N99" s="75"/>
+    </row>
+    <row r="100" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="77"/>
+      <c r="B100" s="91"/>
+      <c r="C100" s="81"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="91"/>
+      <c r="H100" s="81"/>
+      <c r="I100" s="81"/>
+      <c r="J100" s="81"/>
+      <c r="K100" s="82"/>
+      <c r="L100" s="91"/>
+      <c r="M100" s="81"/>
+      <c r="N100" s="82"/>
       <c r="O100" s="78"/>
     </row>
-    <row r="101" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="79"/>
-      <c r="B101" s="122" t="s">
-        <v>126</v>
-      </c>
+    <row r="101" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="78"/>
+      <c r="B101" s="92"/>
       <c r="C101" s="90"/>
       <c r="D101" s="90"/>
       <c r="E101" s="90"/>
-      <c r="F101" s="103"/>
-      <c r="G101" s="122" t="s">
-        <v>127</v>
-      </c>
+      <c r="F101" s="93"/>
+      <c r="G101" s="92"/>
       <c r="H101" s="90"/>
       <c r="I101" s="90"/>
       <c r="J101" s="90"/>
-      <c r="K101" s="103"/>
-      <c r="L101" s="122" t="s">
-        <v>128</v>
-      </c>
+      <c r="K101" s="93"/>
+      <c r="L101" s="92"/>
       <c r="M101" s="90"/>
-      <c r="N101" s="103"/>
-      <c r="O101" s="1"/>
+      <c r="N101" s="93"/>
+      <c r="O101" s="78"/>
     </row>
     <row r="102" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="B102" s="132" t="s">
-        <v>129</v>
+      <c r="A102" s="79"/>
+      <c r="B102" s="99" t="s">
+        <v>125</v>
       </c>
       <c r="C102" s="81"/>
       <c r="D102" s="81"/>
       <c r="E102" s="81"/>
-      <c r="F102" s="119"/>
-      <c r="G102" s="132" t="s">
-        <v>130</v>
+      <c r="F102" s="82"/>
+      <c r="G102" s="99" t="s">
+        <v>126</v>
       </c>
       <c r="H102" s="81"/>
       <c r="I102" s="81"/>
       <c r="J102" s="81"/>
-      <c r="K102" s="119"/>
-      <c r="L102" s="132" t="s">
-        <v>131</v>
+      <c r="K102" s="82"/>
+      <c r="L102" s="99" t="s">
+        <v>127</v>
       </c>
       <c r="M102" s="81"/>
-      <c r="N102" s="119"/>
+      <c r="N102" s="82"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="60"/>
-      <c r="B103" s="60"/>
-      <c r="C103" s="60"/>
-      <c r="D103" s="60"/>
-      <c r="E103" s="60"/>
-      <c r="F103" s="60"/>
-      <c r="G103" s="60"/>
-      <c r="H103" s="60"/>
-      <c r="I103" s="60"/>
-      <c r="J103" s="60"/>
-      <c r="K103" s="60"/>
-      <c r="L103" s="107"/>
-      <c r="M103" s="107"/>
-      <c r="N103" s="107"/>
-      <c r="O103" s="60"/>
+    <row r="103" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+      <c r="B103" s="86" t="s">
+        <v>128</v>
+      </c>
+      <c r="C103" s="87"/>
+      <c r="D103" s="87"/>
+      <c r="E103" s="87"/>
+      <c r="F103" s="88"/>
+      <c r="G103" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="H103" s="87"/>
+      <c r="I103" s="87"/>
+      <c r="J103" s="87"/>
+      <c r="K103" s="88"/>
+      <c r="L103" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="M103" s="87"/>
+      <c r="N103" s="88"/>
+      <c r="O103" s="1"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="60"/>
@@ -3435,116 +3446,45 @@
       <c r="I104" s="60"/>
       <c r="J104" s="60"/>
       <c r="K104" s="60"/>
-      <c r="L104" s="88"/>
-      <c r="M104" s="88"/>
-      <c r="N104" s="88"/>
+      <c r="L104" s="139"/>
+      <c r="M104" s="139"/>
+      <c r="N104" s="139"/>
       <c r="O104" s="60"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="60"/>
+      <c r="B105" s="60"/>
+      <c r="C105" s="60"/>
+      <c r="D105" s="60"/>
+      <c r="E105" s="60"/>
+      <c r="F105" s="60"/>
+      <c r="G105" s="60"/>
+      <c r="H105" s="60"/>
+      <c r="I105" s="60"/>
+      <c r="J105" s="60"/>
+      <c r="K105" s="60"/>
+      <c r="L105" s="90"/>
+      <c r="M105" s="90"/>
+      <c r="N105" s="90"/>
+      <c r="O105" s="60"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
     </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="124">
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="L102:N102"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="B84:N86"/>
-    <mergeCell ref="B99:F100"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="N30:N34"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B49:M49"/>
-    <mergeCell ref="F66:M66"/>
-    <mergeCell ref="B51:M51"/>
-    <mergeCell ref="B56:N56"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="B73:N73"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B52:M52"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="F62:M62"/>
-    <mergeCell ref="G99:K100"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B43:N43"/>
-    <mergeCell ref="B18:N18"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="B50:M50"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="F61:M61"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G68:M68"/>
-    <mergeCell ref="B44:N44"/>
-    <mergeCell ref="G9:N9"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B83:N83"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="B27:N27"/>
-    <mergeCell ref="B45:M45"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B47:M47"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="B67:N67"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="B46:M46"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F60:M60"/>
-    <mergeCell ref="F57:M57"/>
-    <mergeCell ref="K42:N42"/>
-    <mergeCell ref="B48:M48"/>
-    <mergeCell ref="G12:N12"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="F63:M63"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="F59:M59"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="G101:K101"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="L101:N101"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="L99:N100"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B55:N55"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="G11:N11"/>
-    <mergeCell ref="N69:N71"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="N103:N104"/>
+  <mergeCells count="125">
+    <mergeCell ref="N104:N105"/>
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="H29:J29"/>
-    <mergeCell ref="M103:M104"/>
-    <mergeCell ref="B54:M54"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="B55:M55"/>
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B32:C32"/>
@@ -3552,28 +3492,117 @@
     <mergeCell ref="K29:M29"/>
     <mergeCell ref="H19:N19"/>
     <mergeCell ref="C41:H41"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B15:N17"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="G103:K103"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="F65:M65"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="G102:K102"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="L102:N102"/>
     <mergeCell ref="G77:H77"/>
-    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="L100:N101"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B56:N56"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="G11:N11"/>
+    <mergeCell ref="N70:N72"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="F66:M66"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="B75:N75"/>
+    <mergeCell ref="N77:N82"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B54:M54"/>
+    <mergeCell ref="B36:N36"/>
+    <mergeCell ref="G76:M76"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="F64:M64"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="G8:N8"/>
     <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B15:N17"/>
-    <mergeCell ref="L103:L104"/>
-    <mergeCell ref="G102:K102"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="F64:M64"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F65:M65"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="B74:N74"/>
-    <mergeCell ref="N76:N81"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B53:M53"/>
-    <mergeCell ref="B36:N36"/>
-    <mergeCell ref="G75:M75"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="F60:M60"/>
+    <mergeCell ref="B35:N35"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C38:H38"/>
+    <mergeCell ref="B53:M53"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G69:M69"/>
+    <mergeCell ref="B44:N44"/>
+    <mergeCell ref="G9:N9"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B84:N84"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B27:N27"/>
+    <mergeCell ref="B45:M45"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="F59:M59"/>
+    <mergeCell ref="B68:N68"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="B46:M46"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F61:M61"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="K42:N42"/>
+    <mergeCell ref="B48:M48"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="F63:M63"/>
+    <mergeCell ref="G100:K101"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B43:N43"/>
+    <mergeCell ref="B18:N18"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="B50:M50"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="F62:M62"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B85:N87"/>
+    <mergeCell ref="B100:F101"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="N30:N34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="B49:M49"/>
+    <mergeCell ref="F67:M67"/>
+    <mergeCell ref="B51:M51"/>
+    <mergeCell ref="B57:N57"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="B74:N74"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="B52:M52"/>
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H20:N20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
